--- a/Tools/DataTablesTool/DataTables/Datas_Gen/#SoundGroup.xlsx
+++ b/Tools/DataTablesTool/DataTables/Datas_Gen/#SoundGroup.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\AltasTest\Tools\DataTablesTool\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\ProjectGroup\CommandoRobot\Tools\DataTablesTool\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8">
